--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251219_201228.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251219_201228.xlsx
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251219_201228.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251219_201228.xlsx
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
